--- a/data/trans_orig/IP07A05-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A05-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2007 (tasa de respuesta: 99,7%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2007 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>25560</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26703</t>
+          <t>26617</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33678</t>
+          <t>33141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49068</t>
+          <t>48267</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>54,39%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19069</t>
+          <t>19040</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30677</t>
+          <t>30509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23386</t>
+          <t>23286</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35025</t>
+          <t>35487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50770</t>
+          <t>51056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,54%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7506</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>9086</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>16624</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>18307</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30236</t>
+          <t>30938</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>50,18%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9392</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22649</t>
+          <t>22565</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26132</t>
+          <t>25361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37978</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>62,52%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>472</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>9803</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>11147</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20169</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21178</t>
+          <t>21321</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23327</t>
+          <t>23944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38066</t>
+          <t>38489</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,97%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12318</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21540</t>
+          <t>21625</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23375</t>
+          <t>22918</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34835</t>
+          <t>34381</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53251</t>
+          <t>53502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>61,12%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>15405</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15240</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25109</t>
+          <t>24740</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39169</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31669</t>
+          <t>32508</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47087</t>
+          <t>47172</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60897</t>
+          <t>61494</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81644</t>
+          <t>81399</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39443</t>
+          <t>39823</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54196</t>
+          <t>54923</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34536</t>
+          <t>34754</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49536</t>
+          <t>50006</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>79002</t>
+          <t>79514</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>100654</t>
+          <t>101767</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,6%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>17934</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>13243</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26577</t>
+          <t>27379</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14254</t>
+          <t>13495</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25663</t>
+          <t>24796</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26223</t>
+          <t>25686</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39185</t>
+          <t>39411</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>43362</t>
+          <t>43223</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>61797</t>
+          <t>61190</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20439</t>
+          <t>20626</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>32317</t>
+          <t>32522</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>26726</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39834</t>
+          <t>40098</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>51297</t>
+          <t>51141</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>69493</t>
+          <t>68847</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>10851</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10846</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21094</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18861</t>
+          <t>18668</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>22590</t>
+          <t>23067</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>37087</t>
+          <t>36097</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>16483</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26904</t>
+          <t>27070</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22406</t>
+          <t>22800</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>32628</t>
+          <t>32119</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>46804</t>
+          <t>46230</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>59,54%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>100293</t>
+          <t>101214</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>127410</t>
+          <t>127614</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>119930</t>
+          <t>121481</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>148690</t>
+          <t>148026</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>228971</t>
+          <t>229615</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>267325</t>
+          <t>268464</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>137771</t>
+          <t>137434</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>165935</t>
+          <t>164922</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>145485</t>
+          <t>146631</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>174495</t>
+          <t>173592</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>291774</t>
+          <t>290411</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>330471</t>
+          <t>331722</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,23%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>19233</t>
+          <t>19470</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>33992</t>
+          <t>34717</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>21462</t>
+          <t>22218</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>38734</t>
+          <t>38808</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>45806</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>67031</t>
+          <t>68347</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>11436</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>13407</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23477</t>
+          <t>24082</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>18054</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24604</t>
+          <t>24695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38655</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,59%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20762</t>
+          <t>20728</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12042</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21681</t>
+          <t>21597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25615</t>
+          <t>25386</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39678</t>
+          <t>39931</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15028</t>
+          <t>15071</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9832</t>
+          <t>9711</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19328</t>
+          <t>19643</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12517</t>
+          <t>11897</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21957</t>
+          <t>21896</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25934</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38701</t>
+          <t>39264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,79%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22384</t>
+          <t>22653</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19116</t>
+          <t>19507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24991</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37895</t>
+          <t>38645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16132</t>
+          <t>16734</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19036</t>
+          <t>18890</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32606</t>
+          <t>31473</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23849</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33831</t>
+          <t>33431</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21920</t>
+          <t>20899</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38434</t>
+          <t>39597</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52650</t>
+          <t>52530</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,82%</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>605</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26111</t>
+          <t>25724</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40623</t>
+          <t>40512</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28316</t>
+          <t>29859</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45157</t>
+          <t>45254</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58928</t>
+          <t>59223</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80704</t>
+          <t>81332</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,81%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39207</t>
+          <t>39241</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54390</t>
+          <t>54420</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>43894</t>
+          <t>42415</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>60456</t>
+          <t>59055</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>87027</t>
+          <t>87295</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>109316</t>
+          <t>109891</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>59,19%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>13753</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21619</t>
+          <t>21977</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16033</t>
+          <t>15643</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28805</t>
+          <t>28798</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19830</t>
+          <t>19389</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32734</t>
+          <t>32716</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39148</t>
+          <t>39066</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>58501</t>
+          <t>57640</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>38,91%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38410</t>
+          <t>38026</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>52590</t>
+          <t>52607</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30504</t>
+          <t>29962</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>43438</t>
+          <t>43814</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>72354</t>
+          <t>73401</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>92593</t>
+          <t>92207</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10862</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6694</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18036</t>
+          <t>16977</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>660</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,82 +8822,82 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>4024</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>7466</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
           <t>0,88%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>1298</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>3936</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>3399</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>1308</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>7655</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8807</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17286</t>
+          <t>17165</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>11919</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>23746</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>18949</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>16577</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>26289</t>
+          <t>26778</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>30485</t>
+          <t>29552</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>43154</t>
+          <t>42537</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,0%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>433</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2384</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>93679</t>
+          <t>92843</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>119857</t>
+          <t>120845</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>104356</t>
+          <t>103550</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>132113</t>
+          <t>131838</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>205074</t>
+          <t>205466</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>246521</t>
+          <t>244447</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>154391</t>
+          <t>154753</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>183075</t>
+          <t>183157</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>144268</t>
+          <t>143464</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>174209</t>
+          <t>172172</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>306688</t>
+          <t>308099</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>349038</t>
+          <t>348599</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,66%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>16333</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>31805</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>17768</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>33020</t>
+          <t>33081</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>37638</t>
+          <t>37548</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>59711</t>
+          <t>59990</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9732</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>13656</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>12741</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2016 (tasa de respuesta: 98,62%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2016 (tasa de respuesta: 98,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14289</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24256</t>
+          <t>23743</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19950</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27123</t>
+          <t>27140</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41142</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,95%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8686</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24653</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26929</t>
+          <t>26354</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40347</t>
+          <t>40447</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>740</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16993</t>
+          <t>16600</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28410</t>
+          <t>28541</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20462</t>
+          <t>20837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32061</t>
+          <t>31768</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40763</t>
+          <t>41046</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58039</t>
+          <t>57421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>20749</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32893</t>
+          <t>32999</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15135</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26653</t>
+          <t>26458</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37303</t>
+          <t>39721</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54744</t>
+          <t>55497</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,99%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>792</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16342</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19789</t>
+          <t>20254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20068</t>
+          <t>20239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33031</t>
+          <t>33203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,48%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16738</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29178</t>
+          <t>29274</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29491</t>
+          <t>29612</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42623</t>
+          <t>42906</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,65%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6219</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7527</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36289</t>
+          <t>36767</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53036</t>
+          <t>53823</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42031</t>
+          <t>41912</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58945</t>
+          <t>58754</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>83158</t>
+          <t>82499</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107338</t>
+          <t>106785</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,15%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47578</t>
+          <t>46963</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>64995</t>
+          <t>65651</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37688</t>
+          <t>37428</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>55069</t>
+          <t>55073</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>89962</t>
+          <t>89129</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>113867</t>
+          <t>114723</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18727</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23767</t>
+          <t>24017</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28172</t>
+          <t>28023</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42511</t>
+          <t>42626</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>29348</t>
+          <t>29286</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44135</t>
+          <t>43901</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62398</t>
+          <t>61787</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>82767</t>
+          <t>82790</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,35%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26549</t>
+          <t>26785</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40613</t>
+          <t>41262</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23508</t>
+          <t>25388</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>54837</t>
+          <t>55169</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>74960</t>
+          <t>75727</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10625</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10517</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>17211</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>19185</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>15548</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25849</t>
+          <t>25549</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>28819</t>
+          <t>29137</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42765</t>
+          <t>42510</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,0%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>10725</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19946</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18025</t>
+          <t>18229</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>20280</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>34169</t>
+          <t>34317</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,43%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -14650,7 +14650,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>132906</t>
+          <t>133279</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>163508</t>
+          <t>162571</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>148353</t>
+          <t>147384</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>179700</t>
+          <t>179745</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>291838</t>
+          <t>291107</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>333027</t>
+          <t>334000</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,16%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>143511</t>
+          <t>143164</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>173936</t>
+          <t>172757</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>138800</t>
+          <t>139794</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>170669</t>
+          <t>170414</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>289306</t>
+          <t>291574</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>331194</t>
+          <t>333597</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>34397</t>
+          <t>34959</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10611</t>
+          <t>10544</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>23803</t>
+          <t>24509</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>32182</t>
+          <t>32271</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>52961</t>
+          <t>53725</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>16823</t>
+          <t>16026</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -15297,7 +15297,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,44 +15312,44 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>4867</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>4772</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
